--- a/mis-portal/reports/2026-06-08/Rajani_Corp_20260608.xlsx
+++ b/mis-portal/reports/2026-06-08/Rajani_Corp_20260608.xlsx
@@ -708,7 +708,7 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Report generated on 08 Jun 2026 10:06 UTC  |  MF data auto-populated from CAS  |  Manual inputs as last updated in portal</t>
+          <t>Report generated on 08 Jun 2026 11:25 UTC  |  MF data auto-populated from CAS  |  Manual inputs as last updated in portal</t>
         </is>
       </c>
     </row>
